--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/178.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/178.xlsx
@@ -426,13 +426,13 @@
         <v>3.478763589934892</v>
       </c>
       <c r="E2">
-        <v>-16.63670535761295</v>
+        <v>-13.99241164421003</v>
       </c>
       <c r="F2">
-        <v>-1.082667230665031</v>
+        <v>-1.133071730390575</v>
       </c>
       <c r="G2">
-        <v>-10.95290465134612</v>
+        <v>-7.49912835931837</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>3.507821340391158</v>
       </c>
       <c r="E3">
-        <v>-16.26529350492585</v>
+        <v>-14.48465224036979</v>
       </c>
       <c r="F3">
-        <v>-1.164461056384857</v>
+        <v>-1.048422522233299</v>
       </c>
       <c r="G3">
-        <v>-11.56528605465497</v>
+        <v>-7.077139740518549</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>3.62235009303241</v>
       </c>
       <c r="E4">
-        <v>-17.74105525691551</v>
+        <v>-14.21550238772391</v>
       </c>
       <c r="F4">
-        <v>-1.122008055358785</v>
+        <v>-1.408381293445796</v>
       </c>
       <c r="G4">
-        <v>-9.995604129391692</v>
+        <v>-6.812441761380582</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>3.818367473626207</v>
       </c>
       <c r="E5">
-        <v>-18.71138949643507</v>
+        <v>-14.97359610745197</v>
       </c>
       <c r="F5">
-        <v>-1.635301774666485</v>
+        <v>-1.520535612845627</v>
       </c>
       <c r="G5">
-        <v>-9.347687330264311</v>
+        <v>-5.99346576369352</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>4.090619202796671</v>
       </c>
       <c r="E6">
-        <v>-18.48215814216679</v>
+        <v>-15.67203623907699</v>
       </c>
       <c r="F6">
-        <v>-1.297189536968019</v>
+        <v>-1.292567246860397</v>
       </c>
       <c r="G6">
-        <v>-10.16923231128985</v>
+        <v>-6.382504522740973</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>4.424804371184925</v>
       </c>
       <c r="E7">
-        <v>-18.66985886131072</v>
+        <v>-16.4047705043621</v>
       </c>
       <c r="F7">
-        <v>-1.501758180558968</v>
+        <v>-1.247886765888198</v>
       </c>
       <c r="G7">
-        <v>-9.156069643905756</v>
+        <v>-5.412024718994703</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>4.811217001681397</v>
       </c>
       <c r="E8">
-        <v>-20.07547907939557</v>
+        <v>-16.4672317463499</v>
       </c>
       <c r="F8">
-        <v>-1.713197303388736</v>
+        <v>-1.391829684370459</v>
       </c>
       <c r="G8">
-        <v>-9.520332280137303</v>
+        <v>-5.064765044652852</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>5.23148463786872</v>
       </c>
       <c r="E9">
-        <v>-19.7022558371054</v>
+        <v>-17.12038713789822</v>
       </c>
       <c r="F9">
-        <v>-1.608507402655532</v>
+        <v>-1.321791220463761</v>
       </c>
       <c r="G9">
-        <v>-9.001831327231111</v>
+        <v>-5.414924756887104</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>5.663746460808835</v>
       </c>
       <c r="E10">
-        <v>-20.78912582673835</v>
+        <v>-18.54571527486445</v>
       </c>
       <c r="F10">
-        <v>-1.449537899486487</v>
+        <v>-1.248216456114512</v>
       </c>
       <c r="G10">
-        <v>-7.789092422012054</v>
+        <v>-3.857048237016869</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>6.084634602303446</v>
       </c>
       <c r="E11">
-        <v>-20.7410379612509</v>
+        <v>-18.63805991682886</v>
       </c>
       <c r="F11">
-        <v>-1.197164173079978</v>
+        <v>-1.36985061207198</v>
       </c>
       <c r="G11">
-        <v>-7.905285949349394</v>
+        <v>-4.130605236017926</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>6.470738412149564</v>
       </c>
       <c r="E12">
-        <v>-22.08195081424014</v>
+        <v>-19.5537128327058</v>
       </c>
       <c r="F12">
-        <v>-0.9350041141767965</v>
+        <v>-1.529542451616266</v>
       </c>
       <c r="G12">
-        <v>-6.163856232054268</v>
+        <v>-3.710086499437543</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>6.795450957230603</v>
       </c>
       <c r="E13">
-        <v>-21.98939333399737</v>
+        <v>-18.98099672495573</v>
       </c>
       <c r="F13">
-        <v>-0.858484503710595</v>
+        <v>-1.192706728085514</v>
       </c>
       <c r="G13">
-        <v>-6.814868391260869</v>
+        <v>-3.449063225848167</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>7.037221392387675</v>
       </c>
       <c r="E14">
-        <v>-22.81510169913396</v>
+        <v>-20.3005487660508</v>
       </c>
       <c r="F14">
-        <v>-0.7660552689062261</v>
+        <v>-1.032770520157403</v>
       </c>
       <c r="G14">
-        <v>-5.661669647565604</v>
+        <v>-2.858736676921946</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>7.185077825148015</v>
       </c>
       <c r="E15">
-        <v>-24.65762908947885</v>
+        <v>-20.82898545495386</v>
       </c>
       <c r="F15">
-        <v>-1.101322064576076</v>
+        <v>-0.8536526366500655</v>
       </c>
       <c r="G15">
-        <v>-6.813696458139966</v>
+        <v>-2.134008600192395</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>7.232681772101587</v>
       </c>
       <c r="E16">
-        <v>-23.18810757467176</v>
+        <v>-22.01030129849078</v>
       </c>
       <c r="F16">
-        <v>-0.6071462365575858</v>
+        <v>-0.8741671553803952</v>
       </c>
       <c r="G16">
-        <v>-5.491550643939076</v>
+        <v>-1.459306177106769</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>7.181732647048067</v>
       </c>
       <c r="E17">
-        <v>-24.8559128523787</v>
+        <v>-22.62081205030887</v>
       </c>
       <c r="F17">
-        <v>-1.187646231621812</v>
+        <v>-0.4342643028585234</v>
       </c>
       <c r="G17">
-        <v>-5.74685329483659</v>
+        <v>-1.034967070974067</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>7.041031267065546</v>
       </c>
       <c r="E18">
-        <v>-26.27689365429756</v>
+        <v>-23.64976285738371</v>
       </c>
       <c r="F18">
-        <v>-0.428547739411804</v>
+        <v>-0.5439616845416507</v>
       </c>
       <c r="G18">
-        <v>-4.707590286420883</v>
+        <v>-0.9992264213320956</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>6.821528625702491</v>
       </c>
       <c r="E19">
-        <v>-26.16716872909171</v>
+        <v>-23.73148822780014</v>
       </c>
       <c r="F19">
-        <v>0.043647359573401</v>
+        <v>-0.3622891159640799</v>
       </c>
       <c r="G19">
-        <v>-5.07985451122085</v>
+        <v>-1.026362963117502</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>6.531887069822083</v>
       </c>
       <c r="E20">
-        <v>-26.37689141733494</v>
+        <v>-24.41656483262853</v>
       </c>
       <c r="F20">
-        <v>-0.2016413404369634</v>
+        <v>0.07710926080948703</v>
       </c>
       <c r="G20">
-        <v>-4.738931221041164</v>
+        <v>-0.1678491200549224</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>6.186314602368247</v>
       </c>
       <c r="E21">
-        <v>-27.04248199850832</v>
+        <v>-24.90204894556884</v>
       </c>
       <c r="F21">
-        <v>0.06527437572569049</v>
+        <v>0.176999600810871</v>
       </c>
       <c r="G21">
-        <v>-4.702422524834081</v>
+        <v>-0.3223291065539338</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>5.796995733118385</v>
       </c>
       <c r="E22">
-        <v>-27.46697662351334</v>
+        <v>-25.46204004135736</v>
       </c>
       <c r="F22">
-        <v>0.3432993271272886</v>
+        <v>0.2844910401003433</v>
       </c>
       <c r="G22">
-        <v>-4.073657231651383</v>
+        <v>-0.2997710492493399</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>5.372166344729536</v>
       </c>
       <c r="E23">
-        <v>-28.06063692354888</v>
+        <v>-25.50291404775059</v>
       </c>
       <c r="F23">
-        <v>-0.2738194773450927</v>
+        <v>0.5638488346530457</v>
       </c>
       <c r="G23">
-        <v>-4.113615516310387</v>
+        <v>-0.2696848113884434</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>4.92365842573427</v>
       </c>
       <c r="E24">
-        <v>-28.30405598688318</v>
+        <v>-26.3350664314001</v>
       </c>
       <c r="F24">
-        <v>0.4468129461485176</v>
+        <v>0.6444365574343957</v>
       </c>
       <c r="G24">
-        <v>-4.624181091558945</v>
+        <v>-0.5703187623551991</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>4.462667574743115</v>
       </c>
       <c r="E25">
-        <v>-29.2676337431833</v>
+        <v>-26.18952580526758</v>
       </c>
       <c r="F25">
-        <v>-0.03721041098126154</v>
+        <v>0.3061122576808131</v>
       </c>
       <c r="G25">
-        <v>-4.089640545514984</v>
+        <v>-1.116929557435343</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>3.995981651797992</v>
       </c>
       <c r="E26">
-        <v>-29.59218041836502</v>
+        <v>-26.58861116261555</v>
       </c>
       <c r="F26">
-        <v>0.1191522199711731</v>
+        <v>0.6663021433986914</v>
       </c>
       <c r="G26">
-        <v>-3.143903759129227</v>
+        <v>-1.153855382380374</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>3.527147343922568</v>
       </c>
       <c r="E27">
-        <v>-29.34762017958078</v>
+        <v>-25.76084234180547</v>
       </c>
       <c r="F27">
-        <v>-0.2069801683480062</v>
+        <v>0.7256869741379851</v>
       </c>
       <c r="G27">
-        <v>-4.869965924031057</v>
+        <v>-1.30086677814279</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>3.06728061230055</v>
       </c>
       <c r="E28">
-        <v>-29.26746166117101</v>
+        <v>-25.85570481531815</v>
       </c>
       <c r="F28">
-        <v>0.2736634497783509</v>
+        <v>0.5350754929168049</v>
       </c>
       <c r="G28">
-        <v>-5.004152266374335</v>
+        <v>-1.989834341957134</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>2.619796708120049</v>
       </c>
       <c r="E29">
-        <v>-28.9527236606899</v>
+        <v>-26.78562695279326</v>
       </c>
       <c r="F29">
-        <v>0.1772456259295025</v>
+        <v>0.4757975215724723</v>
       </c>
       <c r="G29">
-        <v>-3.755076813316238</v>
+        <v>-2.031262508835574</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>2.184966878823589</v>
       </c>
       <c r="E30">
-        <v>-29.95905700433343</v>
+        <v>-26.23945223120215</v>
       </c>
       <c r="F30">
-        <v>0.3282768842775195</v>
+        <v>0.3592520265704015</v>
       </c>
       <c r="G30">
-        <v>-4.659458264825419</v>
+        <v>-2.07011507128446</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>1.768131860320506</v>
       </c>
       <c r="E31">
-        <v>-28.18957616396928</v>
+        <v>-25.8500623367046</v>
       </c>
       <c r="F31">
-        <v>0.4341588057033524</v>
+        <v>0.3286231418518897</v>
       </c>
       <c r="G31">
-        <v>-5.105915125705993</v>
+        <v>-2.31045405634447</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>1.371998572299763</v>
       </c>
       <c r="E32">
-        <v>-28.85368593414215</v>
+        <v>-26.77090941226833</v>
       </c>
       <c r="F32">
-        <v>0.2631050788622684</v>
+        <v>0.674934560103265</v>
       </c>
       <c r="G32">
-        <v>-5.411134182244639</v>
+        <v>-2.532320197295347</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>0.9951395947354461</v>
       </c>
       <c r="E33">
-        <v>-28.53090083534942</v>
+        <v>-25.45547828252025</v>
       </c>
       <c r="F33">
-        <v>-0.4304662383166876</v>
+        <v>0.8271619809809245</v>
       </c>
       <c r="G33">
-        <v>-3.809793509989313</v>
+        <v>-2.478891302837049</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>0.6355134896397607</v>
       </c>
       <c r="E34">
-        <v>-27.22453118209068</v>
+        <v>-25.30505596140746</v>
       </c>
       <c r="F34">
-        <v>0.001912553085556306</v>
+        <v>0.5945017420262386</v>
       </c>
       <c r="G34">
-        <v>-4.759363908109545</v>
+        <v>-2.232626441261744</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>0.2974669242695165</v>
       </c>
       <c r="E35">
-        <v>-27.91941646161968</v>
+        <v>-24.97757030659476</v>
       </c>
       <c r="F35">
-        <v>0.1845534831569997</v>
+        <v>0.6777891141733121</v>
       </c>
       <c r="G35">
-        <v>-5.523477545119807</v>
+        <v>-2.315413253562299</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.02148161977493085</v>
       </c>
       <c r="E36">
-        <v>-26.96502245060712</v>
+        <v>-24.1476866884231</v>
       </c>
       <c r="F36">
-        <v>0.3406220436814406</v>
+        <v>0.6593074090494524</v>
       </c>
       <c r="G36">
-        <v>-5.569643102664943</v>
+        <v>-2.775390382425255</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.3241763299408614</v>
       </c>
       <c r="E37">
-        <v>-26.83957466364664</v>
+        <v>-24.65180094343097</v>
       </c>
       <c r="F37">
-        <v>-0.3023741300869945</v>
+        <v>0.8614862126833249</v>
       </c>
       <c r="G37">
-        <v>-5.279460543965667</v>
+        <v>-2.780213847275973</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.6080082710416426</v>
       </c>
       <c r="E38">
-        <v>-25.55279066047108</v>
+        <v>-22.87736821673943</v>
       </c>
       <c r="F38">
-        <v>0.5323468506919833</v>
+        <v>0.5941115809795201</v>
       </c>
       <c r="G38">
-        <v>-6.049910565138093</v>
+        <v>-2.968074064447456</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-0.8722929631115851</v>
       </c>
       <c r="E39">
-        <v>-26.53355850410431</v>
+        <v>-23.21023822714724</v>
       </c>
       <c r="F39">
-        <v>0.278984881973935</v>
+        <v>0.9065891610309523</v>
       </c>
       <c r="G39">
-        <v>-6.003731765410799</v>
+        <v>-2.093467659518479</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-1.117557080822815</v>
       </c>
       <c r="E40">
-        <v>-24.62441273263258</v>
+        <v>-22.08032509207139</v>
       </c>
       <c r="F40">
-        <v>0.1577765068615057</v>
+        <v>0.5777123915062983</v>
       </c>
       <c r="G40">
-        <v>-5.613213192507292</v>
+        <v>-2.8457758911357</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-1.342383707071777</v>
       </c>
       <c r="E41">
-        <v>-24.27159479422098</v>
+        <v>-22.7931657710408</v>
       </c>
       <c r="F41">
-        <v>0.1854439781150092</v>
+        <v>1.020575829125776</v>
       </c>
       <c r="G41">
-        <v>-5.609253780042323</v>
+        <v>-2.718561557698126</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-1.541910462524987</v>
       </c>
       <c r="E42">
-        <v>-24.98989228436963</v>
+        <v>-21.82839249760266</v>
       </c>
       <c r="F42">
-        <v>0.3560421028845533</v>
+        <v>1.037557360883165</v>
       </c>
       <c r="G42">
-        <v>-5.246970850043259</v>
+        <v>-2.453287543636326</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-1.714640861348377</v>
       </c>
       <c r="E43">
-        <v>-24.86857446570415</v>
+        <v>-21.03811491310209</v>
       </c>
       <c r="F43">
-        <v>-0.00538287863089894</v>
+        <v>0.5360388842062608</v>
       </c>
       <c r="G43">
-        <v>-6.923656228226859</v>
+        <v>-2.890226586091494</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.858049283502465</v>
       </c>
       <c r="E44">
-        <v>-24.49981629878554</v>
+        <v>-20.70265914403589</v>
       </c>
       <c r="F44">
-        <v>0.1964546376330202</v>
+        <v>0.7000125548556173</v>
       </c>
       <c r="G44">
-        <v>-4.959016288491912</v>
+        <v>-2.577697845002137</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.967905626424576</v>
       </c>
       <c r="E45">
-        <v>-23.45818123601521</v>
+        <v>-20.63350934593877</v>
       </c>
       <c r="F45">
-        <v>0.4400733489593408</v>
+        <v>0.896827679556363</v>
       </c>
       <c r="G45">
-        <v>-5.680549688776067</v>
+        <v>-2.891772610858334</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.042289122426816</v>
       </c>
       <c r="E46">
-        <v>-23.03379982286039</v>
+        <v>-19.67538387234389</v>
       </c>
       <c r="F46">
-        <v>0.1164782499949363</v>
+        <v>0.7129036083779832</v>
       </c>
       <c r="G46">
-        <v>-6.193061864801718</v>
+        <v>-2.029756210615206</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.080719977296483</v>
       </c>
       <c r="E47">
-        <v>-22.25781863080203</v>
+        <v>-19.27237232803126</v>
       </c>
       <c r="F47">
-        <v>0.5005756473250111</v>
+        <v>0.6884932777522873</v>
       </c>
       <c r="G47">
-        <v>-5.771804876566078</v>
+        <v>-2.760178425672304</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.083431350453057</v>
       </c>
       <c r="E48">
-        <v>-22.9562859332711</v>
+        <v>-19.16281042788968</v>
       </c>
       <c r="F48">
-        <v>0.5658244909087226</v>
+        <v>0.8573874507742729</v>
       </c>
       <c r="G48">
-        <v>-6.788768050229255</v>
+        <v>-2.084270964010384</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.05226184516374</v>
       </c>
       <c r="E49">
-        <v>-22.199944732984</v>
+        <v>-18.83359942448007</v>
       </c>
       <c r="F49">
-        <v>0.3935348399026618</v>
+        <v>1.163170993843682</v>
       </c>
       <c r="G49">
-        <v>-5.721818949468622</v>
+        <v>-2.145370392483173</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-1.991036712004274</v>
       </c>
       <c r="E50">
-        <v>-19.72008896774761</v>
+        <v>-18.50912067640846</v>
       </c>
       <c r="F50">
-        <v>0.4565719425208986</v>
+        <v>0.7552712875615667</v>
       </c>
       <c r="G50">
-        <v>-6.828272790149377</v>
+        <v>-3.057577973647192</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-1.903657031029682</v>
       </c>
       <c r="E51">
-        <v>-21.10058068356389</v>
+        <v>-18.18798394215452</v>
       </c>
       <c r="F51">
-        <v>0.2038362195593666</v>
+        <v>0.6996878348337199</v>
       </c>
       <c r="G51">
-        <v>-7.248801458366379</v>
+        <v>-2.79849136919829</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-1.795211451036971</v>
       </c>
       <c r="E52">
-        <v>-20.01718856196884</v>
+        <v>-17.77519995093334</v>
       </c>
       <c r="F52">
-        <v>0.6094032432351989</v>
+        <v>0.8321868576463064</v>
       </c>
       <c r="G52">
-        <v>-5.881334275732865</v>
+        <v>-2.85858439182714</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-1.671367433358122</v>
       </c>
       <c r="E53">
-        <v>-20.14695651313264</v>
+        <v>-16.53225610462604</v>
       </c>
       <c r="F53">
-        <v>0.3786921527793002</v>
+        <v>0.7898672237720853</v>
       </c>
       <c r="G53">
-        <v>-6.308967374677142</v>
+        <v>-2.860438297329132</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-1.536647007147042</v>
       </c>
       <c r="E54">
-        <v>-18.72048267224247</v>
+        <v>-16.78094178323126</v>
       </c>
       <c r="F54">
-        <v>0.3413518353633069</v>
+        <v>0.598487017601107</v>
       </c>
       <c r="G54">
-        <v>-7.018983387030173</v>
+        <v>-3.345661646474571</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-1.394634843076095</v>
       </c>
       <c r="E55">
-        <v>-19.17123338954395</v>
+        <v>-16.92025575760323</v>
       </c>
       <c r="F55">
-        <v>0.4978668859178567</v>
+        <v>0.9226661155844852</v>
       </c>
       <c r="G55">
-        <v>-6.151064284090524</v>
+        <v>-2.754365107705344</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-1.249932868065704</v>
       </c>
       <c r="E56">
-        <v>-18.85475192656989</v>
+        <v>-16.60720234945298</v>
       </c>
       <c r="F56">
-        <v>0.550308341086885</v>
+        <v>0.7611709202043048</v>
       </c>
       <c r="G56">
-        <v>-7.596004853434062</v>
+        <v>-3.407502637148156</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-1.105125421968731</v>
       </c>
       <c r="E57">
-        <v>-19.35997565770965</v>
+        <v>-16.23092238720763</v>
       </c>
       <c r="F57">
-        <v>0.427020763793429</v>
+        <v>0.8027715311728959</v>
       </c>
       <c r="G57">
-        <v>-6.871465477800249</v>
+        <v>-3.561350309449167</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-0.9613097771351421</v>
       </c>
       <c r="E58">
-        <v>-18.4762575405348</v>
+        <v>-15.85419410603553</v>
       </c>
       <c r="F58">
-        <v>0.557662586888939</v>
+        <v>0.4676024828565768</v>
       </c>
       <c r="G58">
-        <v>-7.109702266442821</v>
+        <v>-3.406867012404616</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-0.8214010344160252</v>
       </c>
       <c r="E59">
-        <v>-18.14123650497334</v>
+        <v>-15.40416794457527</v>
       </c>
       <c r="F59">
-        <v>0.08867409811997093</v>
+        <v>0.5774787918987088</v>
       </c>
       <c r="G59">
-        <v>-7.303680371770877</v>
+        <v>-3.124229186989338</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-0.6867146429431052</v>
       </c>
       <c r="E60">
-        <v>-17.32828032264235</v>
+        <v>-15.33693369098339</v>
       </c>
       <c r="F60">
-        <v>-0.1819626444160584</v>
+        <v>0.8627635552184417</v>
       </c>
       <c r="G60">
-        <v>-7.395276545751432</v>
+        <v>-3.784381762429867</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-0.5573741300481249</v>
       </c>
       <c r="E61">
-        <v>-18.34886703822502</v>
+        <v>-15.33684764997725</v>
       </c>
       <c r="F61">
-        <v>0.1570425733426253</v>
+        <v>0.9065262051083396</v>
       </c>
       <c r="G61">
-        <v>-7.010375968628067</v>
+        <v>-3.680907351054406</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-0.4335969035183936</v>
       </c>
       <c r="E62">
-        <v>-18.49199398771145</v>
+        <v>-15.02599960866873</v>
       </c>
       <c r="F62">
-        <v>0.467275277732471</v>
+        <v>0.6597108239746157</v>
       </c>
       <c r="G62">
-        <v>-7.509546646130456</v>
+        <v>-3.462259060367701</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-0.3166735822522584</v>
       </c>
       <c r="E63">
-        <v>-17.055317494882</v>
+        <v>-13.88829296982568</v>
       </c>
       <c r="F63">
-        <v>0.06363006643113348</v>
+        <v>0.621781537335232</v>
       </c>
       <c r="G63">
-        <v>-7.402692167759399</v>
+        <v>-3.885681145386026</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-0.2062295832540355</v>
       </c>
       <c r="E64">
-        <v>-17.17707910400024</v>
+        <v>-14.35416426183877</v>
       </c>
       <c r="F64">
-        <v>0.1653096800225644</v>
+        <v>0.5112259670228043</v>
       </c>
       <c r="G64">
-        <v>-7.091682967072568</v>
+        <v>-4.512251546876187</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-0.1018467241723146</v>
       </c>
       <c r="E65">
-        <v>-17.5059595288073</v>
+        <v>-14.26493520999163</v>
       </c>
       <c r="F65">
-        <v>-0.3589400265545615</v>
+        <v>0.6198564114911259</v>
       </c>
       <c r="G65">
-        <v>-8.086243679071497</v>
+        <v>-3.8849793097317</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-0.005426494255106277</v>
       </c>
       <c r="E66">
-        <v>-16.85490534919854</v>
+        <v>-14.48946147976594</v>
       </c>
       <c r="F66">
-        <v>-0.4097827326361868</v>
+        <v>0.4863003918725672</v>
       </c>
       <c r="G66">
-        <v>-8.359085600236071</v>
+        <v>-4.235201922331199</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>0.08301845884379998</v>
       </c>
       <c r="E67">
-        <v>-17.5215465363417</v>
+        <v>-13.92002851567143</v>
       </c>
       <c r="F67">
-        <v>-0.07746823838991472</v>
+        <v>0.1797398401793318</v>
       </c>
       <c r="G67">
-        <v>-7.6599745248894</v>
+        <v>-4.358738239674643</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>0.1646867886587749</v>
       </c>
       <c r="E68">
-        <v>-15.85297141805346</v>
+        <v>-13.62527919946018</v>
       </c>
       <c r="F68">
-        <v>-0.468632438033272</v>
+        <v>0.2073890873499737</v>
       </c>
       <c r="G68">
-        <v>-9.457335909070512</v>
+        <v>-4.236347371087787</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>0.2412715203474873</v>
       </c>
       <c r="E69">
-        <v>-16.22860833698972</v>
+        <v>-14.05688352865723</v>
       </c>
       <c r="F69">
-        <v>-0.1638702719715144</v>
+        <v>0.1901126567971872</v>
       </c>
       <c r="G69">
-        <v>-8.082479588793346</v>
+        <v>-3.63991948673269</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>0.3145642511834045</v>
       </c>
       <c r="E70">
-        <v>-15.97738218446619</v>
+        <v>-14.44909013398756</v>
       </c>
       <c r="F70">
-        <v>-0.4375106747100946</v>
+        <v>0.4165377743110013</v>
       </c>
       <c r="G70">
-        <v>-8.23431113886094</v>
+        <v>-4.348889366695311</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>0.3894875261542903</v>
       </c>
       <c r="E71">
-        <v>-17.19886106397714</v>
+        <v>-13.92875488508421</v>
       </c>
       <c r="F71">
-        <v>-0.3367033319938116</v>
+        <v>0.07925887421975174</v>
       </c>
       <c r="G71">
-        <v>-8.00169234599851</v>
+        <v>-4.312377359942689</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>0.4714835935685114</v>
       </c>
       <c r="E72">
-        <v>-17.25743234679235</v>
+        <v>-12.83314946909047</v>
       </c>
       <c r="F72">
-        <v>-0.6633675321855882</v>
+        <v>0.1943033674879499</v>
       </c>
       <c r="G72">
-        <v>-7.360303942674571</v>
+        <v>-4.178475724515788</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>0.5636309382097283</v>
       </c>
       <c r="E73">
-        <v>-15.38241768391643</v>
+        <v>-13.19384695227542</v>
       </c>
       <c r="F73">
-        <v>-0.4370923491716809</v>
+        <v>0.336459497482373</v>
       </c>
       <c r="G73">
-        <v>-7.866039431981334</v>
+        <v>-4.409664361705252</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>0.6713693522318557</v>
       </c>
       <c r="E74">
-        <v>-16.39656038098619</v>
+        <v>-14.3853518623296</v>
       </c>
       <c r="F74">
-        <v>-0.2909873917681125</v>
+        <v>-0.3612254922188854</v>
       </c>
       <c r="G74">
-        <v>-7.514353558253478</v>
+        <v>-4.692063827841701</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>0.7993899550113118</v>
       </c>
       <c r="E75">
-        <v>-16.80670880033491</v>
+        <v>-15.37458795235717</v>
       </c>
       <c r="F75">
-        <v>-0.3856913234605688</v>
+        <v>-0.3041675455140554</v>
       </c>
       <c r="G75">
-        <v>-7.110318027913126</v>
+        <v>-3.894192557967492</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>0.9498693930882905</v>
       </c>
       <c r="E76">
-        <v>-18.54170304689365</v>
+        <v>-14.82143938079424</v>
       </c>
       <c r="F76">
-        <v>-0.2025334921297785</v>
+        <v>-0.1725697864357148</v>
       </c>
       <c r="G76">
-        <v>-7.769232459321966</v>
+        <v>-4.076875081915555</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>1.123042109283</v>
       </c>
       <c r="E77">
-        <v>-18.1003624985801</v>
+        <v>-15.64967010595311</v>
       </c>
       <c r="F77">
-        <v>-0.411066702110526</v>
+        <v>-0.3519121575092105</v>
       </c>
       <c r="G77">
-        <v>-7.283307274522202</v>
+        <v>-3.442289849674818</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>1.31958169794577</v>
       </c>
       <c r="E78">
-        <v>-17.82761703757213</v>
+        <v>-15.98827316445463</v>
       </c>
       <c r="F78">
-        <v>-0.3085852288731852</v>
+        <v>-0.2791732158693859</v>
       </c>
       <c r="G78">
-        <v>-6.524639484924042</v>
+        <v>-3.807598618296776</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>1.536822832305148</v>
       </c>
       <c r="E79">
-        <v>-17.96213535796997</v>
+        <v>-15.8773210227927</v>
       </c>
       <c r="F79">
-        <v>-0.5581681854996622</v>
+        <v>-0.3029688978822045</v>
       </c>
       <c r="G79">
-        <v>-6.005327448360728</v>
+        <v>-3.701359901396024</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>1.76755286322661</v>
       </c>
       <c r="E80">
-        <v>-19.58151313463889</v>
+        <v>-17.71674640844233</v>
       </c>
       <c r="F80">
-        <v>-0.6824787965355756</v>
+        <v>-0.4176762456174632</v>
       </c>
       <c r="G80">
-        <v>-6.51683652908798</v>
+        <v>-4.475921620128225</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>2.00580175148642</v>
       </c>
       <c r="E81">
-        <v>-20.0204128354623</v>
+        <v>-18.19063309944901</v>
       </c>
       <c r="F81">
-        <v>-0.667847343099928</v>
+        <v>-0.5134023826849742</v>
       </c>
       <c r="G81">
-        <v>-7.121573882746648</v>
+        <v>-3.796015019454866</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>2.242951982952953</v>
       </c>
       <c r="E82">
-        <v>-21.04319133246469</v>
+        <v>-17.80339875857911</v>
       </c>
       <c r="F82">
-        <v>-0.9346296921107311</v>
+        <v>-0.2311560709987098</v>
       </c>
       <c r="G82">
-        <v>-6.431705850545621</v>
+        <v>-3.2949242255397</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>2.468294069279304</v>
       </c>
       <c r="E83">
-        <v>-20.75159383416278</v>
+        <v>-19.34771255009688</v>
       </c>
       <c r="F83">
-        <v>-1.04377123926658</v>
+        <v>-0.4801757377912832</v>
       </c>
       <c r="G83">
-        <v>-7.728502817552313</v>
+        <v>-4.312291285758668</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>2.670446622124442</v>
       </c>
       <c r="E84">
-        <v>-23.29380668648479</v>
+        <v>-20.12909621164639</v>
       </c>
       <c r="F84">
-        <v>-1.382738352124735</v>
+        <v>-0.5901009205101804</v>
       </c>
       <c r="G84">
-        <v>-7.366104018459374</v>
+        <v>-3.85468450750183</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>2.839187777661382</v>
       </c>
       <c r="E85">
-        <v>-22.69152417193864</v>
+        <v>-20.83929679026933</v>
       </c>
       <c r="F85">
-        <v>-1.471512829947952</v>
+        <v>-0.2602723568397096</v>
       </c>
       <c r="G85">
-        <v>-6.373112505046061</v>
+        <v>-3.388761638850342</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>2.963224521589849</v>
       </c>
       <c r="E86">
-        <v>-25.4225653334325</v>
+        <v>-22.86243783793614</v>
       </c>
       <c r="F86">
-        <v>-1.519121589689048</v>
+        <v>-0.5211898646386923</v>
       </c>
       <c r="G86">
-        <v>-5.828885302754191</v>
+        <v>-2.745300834018819</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>3.032607743823588</v>
       </c>
       <c r="E87">
-        <v>-25.6506917400429</v>
+        <v>-23.00407944794805</v>
       </c>
       <c r="F87">
-        <v>-1.375501734493878</v>
+        <v>-1.24666823743868</v>
       </c>
       <c r="G87">
-        <v>-6.435380556094212</v>
+        <v>-3.081049741520625</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>3.039896273321667</v>
       </c>
       <c r="E88">
-        <v>-26.66891912066758</v>
+        <v>-24.46937589650598</v>
       </c>
       <c r="F88">
-        <v>-1.514945789611536</v>
+        <v>-0.8527132680152908</v>
       </c>
       <c r="G88">
-        <v>-7.135885371112916</v>
+        <v>-2.814994438711556</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>2.978654581107172</v>
       </c>
       <c r="E89">
-        <v>-28.76740944734802</v>
+        <v>-25.3901550449596</v>
       </c>
       <c r="F89">
-        <v>-1.482958382352433</v>
+        <v>-1.105574074454646</v>
       </c>
       <c r="G89">
-        <v>-6.588208580369128</v>
+        <v>-3.159628850440765</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>2.845869684878066</v>
       </c>
       <c r="E90">
-        <v>-29.30719449211431</v>
+        <v>-27.87989194048073</v>
       </c>
       <c r="F90">
-        <v>-1.689292276878748</v>
+        <v>-1.302503513856978</v>
       </c>
       <c r="G90">
-        <v>-5.51133446408176</v>
+        <v>-2.485330313910931</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>2.642969055883399</v>
       </c>
       <c r="E91">
-        <v>-28.91993750887437</v>
+        <v>-29.50489408186717</v>
       </c>
       <c r="F91">
-        <v>-1.358076197808588</v>
+        <v>-1.457298045315913</v>
       </c>
       <c r="G91">
-        <v>-5.122656554498087</v>
+        <v>-2.600649857225904</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>2.373430313733799</v>
       </c>
       <c r="E92">
-        <v>-32.43333595382938</v>
+        <v>-30.36174929122852</v>
       </c>
       <c r="F92">
-        <v>-1.374628635251328</v>
+        <v>-1.504182811946962</v>
       </c>
       <c r="G92">
-        <v>-5.642686979443423</v>
+        <v>-3.499025979126848</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>2.043715560769425</v>
       </c>
       <c r="E93">
-        <v>-35.35527040864257</v>
+        <v>-34.16475270592207</v>
       </c>
       <c r="F93">
-        <v>-1.870850530754732</v>
+        <v>-1.559091145241527</v>
       </c>
       <c r="G93">
-        <v>-5.367862041500826</v>
+        <v>-3.280486936442939</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>1.667695840835718</v>
       </c>
       <c r="E94">
-        <v>-35.91688722659985</v>
+        <v>-34.09069404200063</v>
       </c>
       <c r="F94">
-        <v>-1.827081253925612</v>
+        <v>-1.637345357049191</v>
       </c>
       <c r="G94">
-        <v>-6.835357357603418</v>
+        <v>-2.81134290698174</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>1.259480611467054</v>
       </c>
       <c r="E95">
-        <v>-37.67143995239772</v>
+        <v>-36.82832866164965</v>
       </c>
       <c r="F95">
-        <v>-2.496450989064378</v>
+        <v>-1.978559002303738</v>
       </c>
       <c r="G95">
-        <v>-6.124136306674092</v>
+        <v>-3.400209505325142</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>0.8347258673984277</v>
       </c>
       <c r="E96">
-        <v>-41.39687287157688</v>
+        <v>-38.40034765714635</v>
       </c>
       <c r="F96">
-        <v>-2.17729345427677</v>
+        <v>-2.370821617123207</v>
       </c>
       <c r="G96">
-        <v>-6.257177200260784</v>
+        <v>-3.804185445845787</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>0.4131721050354779</v>
       </c>
       <c r="E97">
-        <v>-42.06146945270558</v>
+        <v>-40.59268155068774</v>
       </c>
       <c r="F97">
-        <v>-2.027227243953015</v>
+        <v>-2.779121424860875</v>
       </c>
       <c r="G97">
-        <v>-6.357867442837716</v>
+        <v>-3.379886066259556</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>0.01443730422208803</v>
       </c>
       <c r="E98">
-        <v>-45.10870678331101</v>
+        <v>-41.87322758091774</v>
       </c>
       <c r="F98">
-        <v>-3.444358435027075</v>
+        <v>-2.776882347771108</v>
       </c>
       <c r="G98">
-        <v>-7.090203153216514</v>
+        <v>-3.724788632177446</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-0.3436859801486789</v>
       </c>
       <c r="E99">
-        <v>-45.47251079966522</v>
+        <v>-45.38615732881296</v>
       </c>
       <c r="F99">
-        <v>-3.304005660868546</v>
+        <v>-2.895874011713646</v>
       </c>
       <c r="G99">
-        <v>-7.314224459313456</v>
+        <v>-4.130598614926847</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-0.6499353829274559</v>
       </c>
       <c r="E100">
-        <v>-48.35646947145009</v>
+        <v>-46.33339408665639</v>
       </c>
       <c r="F100">
-        <v>-3.346972249684353</v>
+        <v>-3.328057308408829</v>
       </c>
       <c r="G100">
-        <v>-8.580978225551261</v>
+        <v>-4.765243436987291</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-0.8864628453314883</v>
       </c>
       <c r="E101">
-        <v>-49.77218592233503</v>
+        <v>-49.4398944244817</v>
       </c>
       <c r="F101">
-        <v>-3.39178775454321</v>
+        <v>-3.331505801906684</v>
       </c>
       <c r="G101">
-        <v>-7.169583414157159</v>
+        <v>-4.805082542006881</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-1.052733641732631</v>
       </c>
       <c r="E102">
-        <v>-51.99119365990011</v>
+        <v>-51.14447204324942</v>
       </c>
       <c r="F102">
-        <v>-3.723600258143385</v>
+        <v>-3.56242315584588</v>
       </c>
       <c r="G102">
-        <v>-8.173688428945805</v>
+        <v>-5.144314143415999</v>
       </c>
     </row>
   </sheetData>
